--- a/data/Projects.xlsx
+++ b/data/Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Proyectos/Proyectos Generales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="624" documentId="8_{1470795A-59F1-784B-99FC-5B46A05E445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8388C1B7-8765-AE45-8D75-CE8E7BD134EB}"/>
+  <xr:revisionPtr revIDLastSave="643" documentId="8_{1470795A-59F1-784B-99FC-5B46A05E445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{159F79EF-4831-D544-A840-1B5BFB864DCB}"/>
   <bookViews>
-    <workbookView xWindow="-35600" yWindow="1200" windowWidth="38400" windowHeight="21000" xr2:uid="{27D03A76-C657-D54E-8770-E03299BC1360}"/>
+    <workbookView xWindow="-38400" yWindow="-1360" windowWidth="38400" windowHeight="21000" xr2:uid="{27D03A76-C657-D54E-8770-E03299BC1360}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="222">
   <si>
     <t>Título proyecto</t>
   </si>
@@ -707,6 +707,21 @@
   <si>
     <t>2023 - 2026</t>
   </si>
+  <si>
+    <t>Building ResIlient Development with GEnerative AI in Education &amp; Agriculture - BRIDGE-AI</t>
+  </si>
+  <si>
+    <t>Fundacio Eurecat, SeamWare, Austria Car, Unniversity of Sousse, Moome, AgroInfoTech, Jomo Kenyata University</t>
+  </si>
+  <si>
+    <t>2026-2029</t>
+  </si>
+  <si>
+    <t>Europeanl</t>
+  </si>
+  <si>
+    <t>HORIZON-CL4-2025-04 (GenAI4Africa)</t>
+  </si>
 </sst>
 </file>
 
@@ -717,7 +732,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="165" formatCode="&quot;BOOL&quot;e&quot;AN&quot;"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -815,13 +830,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -847,7 +855,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -909,7 +917,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="4" builtinId="8"/>
@@ -6804,7 +6811,7 @@
       </c>
       <c r="V9" s="16"/>
     </row>
-    <row r="10" spans="1:1029" ht="166" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1029" ht="151" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>97</v>
       </c>
@@ -8069,30 +8076,76 @@
       </c>
       <c r="M48" s="6"/>
     </row>
-    <row r="49" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A49" s="27"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6"/>
+    <row r="49" spans="1:22" ht="91" x14ac:dyDescent="0.2">
+      <c r="A49" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="F49" s="9">
+        <v>101299050</v>
+      </c>
+      <c r="H49" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="I49" s="13">
+        <v>312500</v>
+      </c>
+      <c r="J49" s="13">
+        <v>312500</v>
+      </c>
+      <c r="K49" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="L49" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="M49" s="11">
+        <v>46143</v>
+      </c>
+      <c r="N49" s="11">
+        <v>47238</v>
+      </c>
+      <c r="O49" s="9">
+        <f t="shared" ref="O49" si="2">DATEDIF(M49,N49+1, "M")</f>
+        <v>36</v>
+      </c>
+      <c r="Q49" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="S49" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="T49" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U49" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="V49" s="16" t="s">
+        <v>221</v>
+      </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C50" s="6"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C51" s="6"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C52" s="6"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C53" s="6"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C54" s="6"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C55" s="6"/>
     </row>
   </sheetData>

--- a/data/Projects.xlsx
+++ b/data/Projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Proyectos/Proyectos Generales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="643" documentId="8_{1470795A-59F1-784B-99FC-5B46A05E445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{159F79EF-4831-D544-A840-1B5BFB864DCB}"/>
+  <xr:revisionPtr revIDLastSave="644" documentId="8_{1470795A-59F1-784B-99FC-5B46A05E445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BEF806F-8C84-F346-861D-37676BD42200}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="-1360" windowWidth="38400" windowHeight="21000" xr2:uid="{27D03A76-C657-D54E-8770-E03299BC1360}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="221">
   <si>
     <t>Título proyecto</t>
   </si>
@@ -715,9 +715,6 @@
   </si>
   <si>
     <t>2026-2029</t>
-  </si>
-  <si>
-    <t>Europeanl</t>
   </si>
   <si>
     <t>HORIZON-CL4-2025-04 (GenAI4Africa)</t>
@@ -8115,7 +8112,7 @@
         <v>36</v>
       </c>
       <c r="Q49" s="9" t="s">
-        <v>220</v>
+        <v>75</v>
       </c>
       <c r="S49" s="9" t="s">
         <v>62</v>
@@ -8127,7 +8124,7 @@
         <v>60</v>
       </c>
       <c r="V49" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.2">

--- a/data/Projects.xlsx
+++ b/data/Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Proyectos/Proyectos Generales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="644" documentId="8_{1470795A-59F1-784B-99FC-5B46A05E445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BEF806F-8C84-F346-861D-37676BD42200}"/>
+  <xr:revisionPtr revIDLastSave="664" documentId="8_{1470795A-59F1-784B-99FC-5B46A05E445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A54ED668-A25B-274E-9399-09FD9032335C}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-1360" windowWidth="38400" windowHeight="21000" xr2:uid="{27D03A76-C657-D54E-8770-E03299BC1360}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{27D03A76-C657-D54E-8770-E03299BC1360}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="225">
   <si>
     <t>Título proyecto</t>
   </si>
@@ -718,6 +718,18 @@
   </si>
   <si>
     <t>HORIZON-CL4-2025-04 (GenAI4Africa)</t>
+  </si>
+  <si>
+    <t>Ecostars Dataspace Fase 2</t>
+  </si>
+  <si>
+    <t>Ecostars Dataspace Phase 2</t>
+  </si>
+  <si>
+    <t>ECOSTARS ESG AI SL</t>
+  </si>
+  <si>
+    <t>Alvaro Alonso</t>
   </si>
 </sst>
 </file>
@@ -8108,7 +8120,7 @@
         <v>47238</v>
       </c>
       <c r="O49" s="9">
-        <f t="shared" ref="O49" si="2">DATEDIF(M49,N49+1, "M")</f>
+        <f t="shared" ref="O49:O50" si="2">DATEDIF(M49,N49+1, "M")</f>
         <v>36</v>
       </c>
       <c r="Q49" s="9" t="s">
@@ -8128,7 +8140,49 @@
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="C50" s="6"/>
+      <c r="A50" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="I50" s="13">
+        <v>48104</v>
+      </c>
+      <c r="J50" s="13">
+        <v>48104</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="L50" s="9">
+        <v>2026</v>
+      </c>
+      <c r="M50" s="11">
+        <v>46113</v>
+      </c>
+      <c r="N50" s="11">
+        <v>46203</v>
+      </c>
+      <c r="O50" s="9">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="Q50" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="S50" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="T50" s="9" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C51" s="6"/>

--- a/data/Projects.xlsx
+++ b/data/Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Proyectos/Proyectos Generales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="664" documentId="8_{1470795A-59F1-784B-99FC-5B46A05E445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A54ED668-A25B-274E-9399-09FD9032335C}"/>
+  <xr:revisionPtr revIDLastSave="678" documentId="8_{1470795A-59F1-784B-99FC-5B46A05E445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{606920B8-5314-444E-9D7C-9F9F549A67AA}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{27D03A76-C657-D54E-8770-E03299BC1360}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17340" xr2:uid="{27D03A76-C657-D54E-8770-E03299BC1360}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="228">
   <si>
     <t>Título proyecto</t>
   </si>
@@ -730,6 +730,15 @@
   </si>
   <si>
     <t>Alvaro Alonso</t>
+  </si>
+  <si>
+    <t>Servicio de Configuración y Adaptación de la Plataforma YODA</t>
+  </si>
+  <si>
+    <t>YODA Platform Configuration and Customization Service</t>
+  </si>
+  <si>
+    <t>INECO</t>
   </si>
 </sst>
 </file>
@@ -4562,7 +4571,7 @@
         <v>154</v>
       </c>
       <c r="I5" s="7">
-        <v>750356</v>
+        <v>1000475</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="6" t="s">
@@ -8120,7 +8129,7 @@
         <v>47238</v>
       </c>
       <c r="O49" s="9">
-        <f t="shared" ref="O49:O50" si="2">DATEDIF(M49,N49+1, "M")</f>
+        <f t="shared" ref="O49:O51" si="2">DATEDIF(M49,N49+1, "M")</f>
         <v>36</v>
       </c>
       <c r="Q49" s="9" t="s">
@@ -8185,7 +8194,43 @@
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="C51" s="6"/>
+      <c r="A51" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="I51" s="13">
+        <v>14816</v>
+      </c>
+      <c r="J51" s="13">
+        <v>14816</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="L51" s="9">
+        <v>2026</v>
+      </c>
+      <c r="M51" s="11">
+        <v>46174</v>
+      </c>
+      <c r="N51" s="11">
+        <v>46203</v>
+      </c>
+      <c r="O51" s="9">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T51" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="U51" s="9" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C52" s="6"/>

--- a/data/Projects.xlsx
+++ b/data/Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Proyectos/Proyectos Generales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="678" documentId="8_{1470795A-59F1-784B-99FC-5B46A05E445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{606920B8-5314-444E-9D7C-9F9F549A67AA}"/>
+  <xr:revisionPtr revIDLastSave="694" documentId="8_{1470795A-59F1-784B-99FC-5B46A05E445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86512D4C-4542-FE4D-AEE4-4A28C50A0D60}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17340" xr2:uid="{27D03A76-C657-D54E-8770-E03299BC1360}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="233">
   <si>
     <t>Título proyecto</t>
   </si>
@@ -739,6 +739,21 @@
   </si>
   <si>
     <t>INECO</t>
+  </si>
+  <si>
+    <t>DEPLOYTOUR</t>
+  </si>
+  <si>
+    <t>2026-2027</t>
+  </si>
+  <si>
+    <t>DEPLOYTOUR is a project co-funded under the EU Digital Europe Programme, supported by DG GROW and DG CONNECT. It is a strategic initiative to boost the competitiveness, sustainability, and resilience of the tourism sector by deploying a trusted Common European Tourism Data Space (ETDS).</t>
+  </si>
+  <si>
+    <t>https://deploytour.eu/the-project/</t>
+  </si>
+  <si>
+    <t>EU Digital Europe Programme</t>
   </si>
 </sst>
 </file>
@@ -873,7 +888,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -935,6 +950,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="4"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="4" builtinId="8"/>
@@ -8232,8 +8248,60 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="C52" s="6"/>
+    <row r="52" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="H52" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="I52" s="13">
+        <v>100000</v>
+      </c>
+      <c r="J52" s="13">
+        <v>100000</v>
+      </c>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="M52" s="11">
+        <v>46174</v>
+      </c>
+      <c r="N52" s="11">
+        <v>46598</v>
+      </c>
+      <c r="O52" s="9">
+        <f t="shared" ref="O52" si="3">DATEDIF(M52,N52+1, "M")</f>
+        <v>13</v>
+      </c>
+      <c r="Q52" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="S52" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="T52" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="U52" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="V52" s="27" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C53" s="6"/>
@@ -8255,6 +8323,8 @@
     <hyperlink ref="E39" r:id="rId7" xr:uid="{101FB994-43AF-FB43-853C-66CC65A113BF}"/>
     <hyperlink ref="E32" r:id="rId8" xr:uid="{6736192C-EE34-C143-96F4-4BC022EAC079}"/>
     <hyperlink ref="E29" r:id="rId9" xr:uid="{D94725B2-C086-D543-ABD9-B51D4F151A2F}"/>
+    <hyperlink ref="E52" r:id="rId10" xr:uid="{0AC78973-4B07-E748-9937-2B11BEA08064}"/>
+    <hyperlink ref="V52" r:id="rId11" display="https://digital-strategy.ec.europa.eu/en/policies/data-spaces" xr:uid="{6021C4A7-2987-514D-A6C9-CFE037CD2F00}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
